--- a/datasets/DataFrame.xlsx
+++ b/datasets/DataFrame.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excel_df" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Excel_dff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Soft</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Node</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>RNA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Cond</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Rep</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Prot</t>
         </is>
@@ -488,51 +481,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1.340379708264428</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.4009630088225484</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -541,51 +539,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>-0.9869413197284669</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -594,51 +597,56 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1.04598747809058</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.7179007099510828</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -647,51 +655,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Amanda</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>-1.345051431116523</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.1387966657108421</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -700,51 +713,56 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Sequest</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.3486149815944181</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.830168364402957</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -753,51 +771,56 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Sequest</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.4799451078992153</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.7876009285539736</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -806,49 +829,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Sequest</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
         <v>0.2375050246349405</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -857,51 +885,56 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Sequest</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-1.245522790665052</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.8965891495010481</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -910,51 +943,56 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>MQ</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Andromeda</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-0.1433677807023918</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.2787576495636448</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -963,51 +1001,56 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>MQ</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Andromeda</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-0.2883182470176846</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.5573902748739504</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -1016,51 +1059,56 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>MQ</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Andromeda</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-0.6038003188109676</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
@@ -1069,51 +1117,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>MQ</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Andromeda</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>CCUGAACCCACUAUUGAUGAG</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1.39807461219245</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.5887548114845748</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>1985-04-06</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0123</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>PEPTIDE</t>
         </is>
